--- a/raw/Feature_lists.xlsx
+++ b/raw/Feature_lists.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -20,10 +20,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>authors</t>
-  </si>
-  <si>
-    <t>number of features</t>
+    <t>description</t>
   </si>
   <si>
     <t>year</t>
@@ -32,6 +29,12 @@
     <t>SAILS</t>
   </si>
   <si>
+    <t>https://sails.clld.org/</t>
+  </si>
+  <si>
+    <t>Pieter Muysken, Harald Hammarström, Olga Krasnoukhova, Neele Müller, Joshua Birchall, Simon van de Kerke, Loretta O'Connor, Swintha Danielsen, Rik van Gijn &amp; George Saad</t>
+  </si>
+  <si>
     <t>WALS</t>
   </si>
   <si>
@@ -47,7 +50,7 @@
     <t>http://grambank.clld.org/</t>
   </si>
   <si>
-    <t>Harald Hammarström, Hedvig Skirgård, et al.</t>
+    <t>Hedvig Skirgård et al.</t>
   </si>
   <si>
     <t>SSWL</t>
@@ -81,13 +84,22 @@
   </si>
   <si>
     <t>Susanne Michaelis, Philippe Maurer, Martin Haspelmath, Magnus Huber</t>
+  </si>
+  <si>
+    <t>ATLAs Zurich</t>
+  </si>
+  <si>
+    <t>https://atlas.evolvinglanguage.ch</t>
+  </si>
+  <si>
+    <t>David Inman et al.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt formatCode="@" numFmtId="165"/>
     <numFmt formatCode="mm/dd/yyyy" numFmtId="166"/>
     <numFmt formatCode="[hh]:mm:ss" numFmtId="167"/>
@@ -129,7 +141,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -154,9 +166,6 @@
       <alignment horizontal="general" vertical="top"/>
     </xf>
     <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0">
-      <alignment horizontal="general" vertical="top"/>
-    </xf>
-    <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="general" vertical="top"/>
     </xf>
     <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
@@ -186,16 +195,22 @@
       <c r="E1" t="s" s="1">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="1">
-        <v>5</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
       <c r="B2" t="s" s="7">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="8">
         <v>6</v>
+      </c>
+      <c r="D2" t="s" s="9">
+        <v>7</v>
+      </c>
+      <c r="E2" s="10">
+        <v>2016</v>
       </c>
     </row>
     <row r="3">
@@ -203,18 +218,15 @@
         <v>3</v>
       </c>
       <c r="B3" t="s" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s" s="9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="10">
-        <v>192</v>
-      </c>
-      <c r="F3" s="11">
         <v>2013</v>
       </c>
     </row>
@@ -223,19 +235,16 @@
         <v>4</v>
       </c>
       <c r="B4" t="s" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s" s="9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="10">
-        <v>195</v>
-      </c>
-      <c r="F4" s="11">
-        <v>2015</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="5">
@@ -243,10 +252,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -254,18 +263,15 @@
         <v>6</v>
       </c>
       <c r="B6" t="s" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s" s="9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="10">
-        <v>304</v>
-      </c>
-      <c r="F6" s="11">
         <v>0</v>
       </c>
     </row>
@@ -274,15 +280,15 @@
         <v>7</v>
       </c>
       <c r="B7" t="s" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s" s="9">
-        <v>20</v>
-      </c>
-      <c r="F7" s="11">
+        <v>21</v>
+      </c>
+      <c r="E7" s="10">
         <v>2017</v>
       </c>
     </row>
@@ -291,16 +297,33 @@
         <v>1</v>
       </c>
       <c r="B8" t="s" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s" s="8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s" s="9">
-        <v>23</v>
-      </c>
-      <c r="F8" s="11">
+        <v>24</v>
+      </c>
+      <c r="E8" s="10">
         <v>2013</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s" s="7">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s" s="8">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s" s="9">
+        <v>27</v>
+      </c>
+      <c r="E9" s="10">
+        <v>2025</v>
       </c>
     </row>
   </sheetData>

--- a/raw/Feature_lists.xlsx
+++ b/raw/Feature_lists.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>id</t>
   </si>
@@ -93,6 +93,15 @@
   </si>
   <si>
     <t>David Inman et al.</t>
+  </si>
+  <si>
+    <t>CrossGram/Nichols1992</t>
+  </si>
+  <si>
+    <t>https://crossgram.clld.org/contributions/nicholsdiversity</t>
+  </si>
+  <si>
+    <t>Nichols, Johanna. 1992. Linguistic diversity in space and time.</t>
   </si>
 </sst>
 </file>
@@ -326,6 +335,23 @@
         <v>2025</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="6">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s" s="7">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s" s="8">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s" s="9">
+        <v>30</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1992</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/raw/Feature_lists.xlsx
+++ b/raw/Feature_lists.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -26,13 +26,28 @@
     <t>year</t>
   </si>
   <si>
+    <t>Collection contributors</t>
+  </si>
+  <si>
+    <t>APiCS</t>
+  </si>
+  <si>
+    <t>APiCS (Atlas of Pidgin and Creole Language Structues) is a collection edited by Susanne Maria Michaelis, Philippe Maurer, Martin Haspelmath, Magnus Huber (https://apics-online.info). It was published by MPI-EVA in 2013, as well as in book form by Oxford University Press. In addition to the four editors, there are over 80 data contributors.</t>
+  </si>
+  <si>
+    <t>Susanne Maria Michaelis, Philippe Maurer, Martin Haspelmath, Magnus Huber</t>
+  </si>
+  <si>
     <t>SAILS</t>
   </si>
   <si>
     <t>https://sails.clld.org/</t>
   </si>
   <si>
-    <t>Pieter Muysken, Harald Hammarström, Olga Krasnoukhova, Neele Müller, Joshua Birchall, Simon van de Kerke, Loretta O'Connor, Swintha Danielsen, Rik van Gijn &amp; George Saad</t>
+    <t>SAILS (South American Indigenous Language Structures Online) is a collection edited  by Muysken, Pieter, Harald Hammarström, Olga Krasnoukhova, Neele Müller, Joshua Birchall, Simon van de Kerke, Loretta O'Connor, Swintha Danielsen, Rik van Gijn and George Saad (https://sails.clld.org/). It was published by by MPI-SHH in 2016.</t>
+  </si>
+  <si>
+    <t>Pieter Muysken, Harald Hammarström, Olga Krasnoukhova, Neele Müller, Joshua Birchall, Simon van de Kerke, Loretta O'Connor, Swintha Danielsen, Rik van Gijn, George Saad</t>
   </si>
   <si>
     <t>WALS</t>
@@ -41,7 +56,10 @@
     <t>http://wals.info</t>
   </si>
   <si>
-    <t>Matthew Dryer, Martin Haspelmath, David Gil, Bernard Comrie</t>
+    <t>WALS (World Atlas of Language Structures) is a collection edited by Matthew Dryer, Martin Haspelmath, David Gil, and Bernard Comrie. It was originally published in 2005 as a book (plus CD-ROM) by Oxford University Press, and online by MPI-EVA since 2008 (subsequent editions in 2011 and 2013) (http://wals.info).</t>
+  </si>
+  <si>
+    <t>Matthew Dryer, Martin Haspelmath, David Gil, Bernard Comrie, Leon Stassen, Anna Siewierska, Dik Bakker, and many others</t>
   </si>
   <si>
     <t>Grambank</t>
@@ -50,40 +68,10 @@
     <t>http://grambank.clld.org/</t>
   </si>
   <si>
-    <t>Hedvig Skirgård et al.</t>
-  </si>
-  <si>
-    <t>SSWL</t>
-  </si>
-  <si>
-    <t>http://sswl.railsplayground.net</t>
-  </si>
-  <si>
-    <t>HG</t>
-  </si>
-  <si>
-    <t>https://huntergatherer.la.utexas.edu/</t>
-  </si>
-  <si>
-    <t>Claire Bowern, Patience Epps, Jane Hill, Keth Hunley</t>
-  </si>
-  <si>
-    <t>DiACL</t>
-  </si>
-  <si>
-    <t>https://diacl.ht.lu.se/</t>
-  </si>
-  <si>
-    <t>Ger Carling et al.</t>
-  </si>
-  <si>
-    <t>APiCS</t>
-  </si>
-  <si>
-    <t>https://apics-online.info</t>
-  </si>
-  <si>
-    <t>Susanne Michaelis, Philippe Maurer, Martin Haspelmath, Magnus Huber</t>
+    <t>Grambank is a dataset collection edited by Hedvig Skirgård and colleagues and published by MPI-EVA in 2023 (http://grambank.clld.org/). The database is described in the release paper (Skirgård et al. 2023). In addition to the feature contributors (called "patrons"), there were dozens of data contributors who collected the data from reference materials.</t>
+  </si>
+  <si>
+    <t>Hedvig Skirgård, Hannah Haynie, Jakob Lesage, Jay Latarche, Alena Witzlack-Makarevich</t>
   </si>
   <si>
     <t>ATLAs Zurich</t>
@@ -92,7 +80,7 @@
     <t>https://atlas.evolvinglanguage.ch</t>
   </si>
   <si>
-    <t>David Inman et al.</t>
+    <t>David Inman et al. (https://atlas.evolvinglanguage.ch)</t>
   </si>
   <si>
     <t>CrossGram/Nichols1992</t>
@@ -101,20 +89,36 @@
     <t>https://crossgram.clld.org/contributions/nicholsdiversity</t>
   </si>
   <si>
-    <t>Nichols, Johanna. 1992. Linguistic diversity in space and time.</t>
+    <t>The CrossGram contribution "Linguistic diversity in space and time" is based on the data from Nichols (1992) (Linguistic diversity in space and time, a book published by The University of Chicago Press). (https://crossgram.clld.org/contributions/nicholsdiversity)</t>
+  </si>
+  <si>
+    <t>Johanna Nichols</t>
+  </si>
+  <si>
+    <t>CrossGram/Haspelmath1997i</t>
+  </si>
+  <si>
+    <t>https://crossgram.clld.org/contributions/haspelmathindefpro</t>
+  </si>
+  <si>
+    <t>The CrossGram contribution "Indefinite pronoun markers" is based on the data from Haspelmath (1997) (Indefinite pronouns, a book published by Oxford University Press). (https://crossgram.clld.org/contributions/haspelmathindefpro)</t>
+  </si>
+  <si>
+    <t>Martin Haspelmath</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt formatCode="@" numFmtId="165"/>
     <numFmt formatCode="mm/dd/yyyy" numFmtId="166"/>
     <numFmt formatCode="[hh]:mm:ss" numFmtId="167"/>
     <numFmt formatCode="@" numFmtId="169"/>
     <numFmt formatCode="@" numFmtId="170"/>
     <numFmt formatCode="@" numFmtId="171"/>
+    <numFmt formatCode="@" numFmtId="173"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -150,7 +154,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -178,6 +182,9 @@
       <alignment horizontal="general" vertical="top"/>
     </xf>
     <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0">
       <alignment horizontal="general" vertical="top"/>
     </xf>
   </cellXfs>
@@ -204,152 +211,139 @@
       <c r="E1" t="s" s="1">
         <v>4</v>
       </c>
+      <c r="F1" t="s" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s" s="7">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="8">
         <v>6</v>
       </c>
       <c r="D2" t="s" s="9">
         <v>7</v>
       </c>
       <c r="E2" s="10">
-        <v>2016</v>
+        <v>2013</v>
+      </c>
+      <c r="F2" t="s" s="11">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s" s="9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="10">
-        <v>2013</v>
+        <v>2016</v>
+      </c>
+      <c r="F3" t="s" s="11">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s" s="7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" s="10">
-        <v>2023</v>
+        <v>2013</v>
+      </c>
+      <c r="F4" t="s" s="11">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s" s="7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s" s="8">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="D5" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="E5" s="10">
+        <v>2023</v>
+      </c>
+      <c r="F5" t="s" s="11">
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s" s="7">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s" s="8">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s" s="9">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E6" s="10">
-        <v>0</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s" s="8">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s" s="9">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E7" s="10">
-        <v>2017</v>
+        <v>1992</v>
+      </c>
+      <c r="F7" t="s" s="11">
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s" s="7">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s" s="8">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s" s="9">
-        <v>24</v>
-      </c>
-      <c r="E8" s="10">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s" s="7">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s" s="8">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s" s="9">
-        <v>27</v>
-      </c>
-      <c r="E9" s="10">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s" s="7">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s" s="8">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s" s="9">
         <v>30</v>
       </c>
-      <c r="E10" s="10">
-        <v>1992</v>
+      <c r="F8" t="s" s="11">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/raw/Feature_lists.xlsx
+++ b/raw/Feature_lists.xlsx
@@ -29,6 +29,42 @@
     <t>Collection contributors</t>
   </si>
   <si>
+    <t>SAILS</t>
+  </si>
+  <si>
+    <t>https://sails.clld.org/</t>
+  </si>
+  <si>
+    <t>SAILS (South American Indigenous Language Structures Online) is a collection edited  by Muysken, Pieter, Harald Hammarström, Olga Krasnoukhova, Neele Müller, Joshua Birchall, Simon van de Kerke, Loretta O'Connor, Swintha Danielsen, Rik van Gijn and George Saad (https://sails.clld.org/). It was published by by MPI-SHH in 2016.</t>
+  </si>
+  <si>
+    <t>Pieter Muysken, Harald Hammarström, Olga Krasnoukhova, Neele Müller, Joshua Birchall, Simon van de Kerke, Loretta O'Connor, Swintha Danielsen, Rik van Gijn, George Saad</t>
+  </si>
+  <si>
+    <t>WALS</t>
+  </si>
+  <si>
+    <t>http://wals.info</t>
+  </si>
+  <si>
+    <t>WALS (World Atlas of Language Structures) is a collection edited by Matthew Dryer, Martin Haspelmath, David Gil, and Bernard Comrie. It was originally published in 2005 as a book (plus CD-ROM) by Oxford University Press, and online by MPI-EVA since 2008 (subsequent editions in 2011 and 2013) (http://wals.info).</t>
+  </si>
+  <si>
+    <t>Matthew Dryer, Martin Haspelmath, David Gil, Bernard Comrie, Leon Stassen, Anna Siewierska, Dik Bakker, and many others</t>
+  </si>
+  <si>
+    <t>Grambank</t>
+  </si>
+  <si>
+    <t>http://grambank.clld.org/</t>
+  </si>
+  <si>
+    <t>Grambank is a dataset collection edited by Hedvig Skirgård and colleagues and published by MPI-EVA in 2023 (http://grambank.clld.org/). The database is described in the release paper (Skirgård et al. 2023). In addition to the feature contributors (called "patrons"), there were dozens of data contributors who collected the data from reference materials.</t>
+  </si>
+  <si>
+    <t>Hedvig Skirgård, Hannah Haynie, Jakob Lesage, Jay Latarche, Alena Witzlack-Makarevich</t>
+  </si>
+  <si>
     <t>APiCS</t>
   </si>
   <si>
@@ -38,42 +74,6 @@
     <t>Susanne Maria Michaelis, Philippe Maurer, Martin Haspelmath, Magnus Huber</t>
   </si>
   <si>
-    <t>SAILS</t>
-  </si>
-  <si>
-    <t>https://sails.clld.org/</t>
-  </si>
-  <si>
-    <t>SAILS (South American Indigenous Language Structures Online) is a collection edited  by Muysken, Pieter, Harald Hammarström, Olga Krasnoukhova, Neele Müller, Joshua Birchall, Simon van de Kerke, Loretta O'Connor, Swintha Danielsen, Rik van Gijn and George Saad (https://sails.clld.org/). It was published by by MPI-SHH in 2016.</t>
-  </si>
-  <si>
-    <t>Pieter Muysken, Harald Hammarström, Olga Krasnoukhova, Neele Müller, Joshua Birchall, Simon van de Kerke, Loretta O'Connor, Swintha Danielsen, Rik van Gijn, George Saad</t>
-  </si>
-  <si>
-    <t>WALS</t>
-  </si>
-  <si>
-    <t>http://wals.info</t>
-  </si>
-  <si>
-    <t>WALS (World Atlas of Language Structures) is a collection edited by Matthew Dryer, Martin Haspelmath, David Gil, and Bernard Comrie. It was originally published in 2005 as a book (plus CD-ROM) by Oxford University Press, and online by MPI-EVA since 2008 (subsequent editions in 2011 and 2013) (http://wals.info).</t>
-  </si>
-  <si>
-    <t>Matthew Dryer, Martin Haspelmath, David Gil, Bernard Comrie, Leon Stassen, Anna Siewierska, Dik Bakker, and many others</t>
-  </si>
-  <si>
-    <t>Grambank</t>
-  </si>
-  <si>
-    <t>http://grambank.clld.org/</t>
-  </si>
-  <si>
-    <t>Grambank is a dataset collection edited by Hedvig Skirgård and colleagues and published by MPI-EVA in 2023 (http://grambank.clld.org/). The database is described in the release paper (Skirgård et al. 2023). In addition to the feature contributors (called "patrons"), there were dozens of data contributors who collected the data from reference materials.</t>
-  </si>
-  <si>
-    <t>Hedvig Skirgård, Hannah Haynie, Jakob Lesage, Jay Latarche, Alena Witzlack-Makarevich</t>
-  </si>
-  <si>
     <t>ATLAs Zurich</t>
   </si>
   <si>
@@ -83,7 +83,7 @@
     <t>David Inman et al. (https://atlas.evolvinglanguage.ch)</t>
   </si>
   <si>
-    <t>CrossGram/Nichols1992</t>
+    <t>CrossGram-Nichols1992</t>
   </si>
   <si>
     <t>https://crossgram.clld.org/contributions/nicholsdiversity</t>
@@ -95,7 +95,7 @@
     <t>Johanna Nichols</t>
   </si>
   <si>
-    <t>CrossGram/Haspelmath1997i</t>
+    <t>CrossGram-Haspelmath1997i</t>
   </si>
   <si>
     <t>https://crossgram.clld.org/contributions/haspelmathindefpro</t>
@@ -217,76 +217,76 @@
     </row>
     <row r="2">
       <c r="A2" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s" s="7">
         <v>6</v>
       </c>
+      <c r="C2" t="s" s="8">
+        <v>7</v>
+      </c>
       <c r="D2" t="s" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="10">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="F2" t="s" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="10">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="F3" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s" s="9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="10">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="F4" t="s" s="11">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s" s="7">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s" s="8">
         <v>18</v>
       </c>
       <c r="D5" t="s" s="9">
         <v>19</v>
       </c>
       <c r="E5" s="10">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="F5" t="s" s="11">
         <v>20</v>
@@ -342,6 +342,9 @@
       <c r="D8" t="s" s="9">
         <v>30</v>
       </c>
+      <c r="E8" s="10">
+        <v>1997</v>
+      </c>
       <c r="F8" t="s" s="11">
         <v>31</v>
       </c>

--- a/raw/Feature_lists.xlsx
+++ b/raw/Feature_lists.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>id</t>
   </si>
@@ -50,7 +50,7 @@
     <t>WALS (World Atlas of Language Structures) is a collection edited by Matthew Dryer, Martin Haspelmath, David Gil, and Bernard Comrie. It was originally published in 2005 as a book (plus CD-ROM) by Oxford University Press, and online by MPI-EVA since 2008 (subsequent editions in 2011 and 2013) (http://wals.info).</t>
   </si>
   <si>
-    <t>Matthew Dryer, Martin Haspelmath, David Gil, Bernard Comrie, Leon Stassen, Anna Siewierska, Dik Bakker, and many others</t>
+    <t>Matthew Dryer, Martin Haspelmath, David Gil, Bernard Comrie, Leon Stassen, Anna Siewierska, Dik Bakker, Balthasar Bickel, Johanna Nichols, Östen Dahl, Ian Maddieson, Johan van der Auwera, Harry van der Hulst, Sonia Cristofaro, Viveka Velupillai, and many others</t>
   </si>
   <si>
     <t>Grambank</t>
@@ -105,6 +105,21 @@
   </si>
   <si>
     <t>Martin Haspelmath</t>
+  </si>
+  <si>
+    <t>UraTyp</t>
+  </si>
+  <si>
+    <t>UraTyp (Uralic Areal Typology Online) is a typological database with 360 features mainly on morphology, syntax, and phonology collected from 35 Uralic languages/language varieties. The database grew out from the cooperation with the Grambank team who set out to collect data from about half of the world's languages. The goal of building the UraTyp database was to create a family-specific database. (URL: https://uralic.clld.org/)</t>
+  </si>
+  <si>
+    <t>Miina Norvik, Yingqi Jing, Michael Dunn, Robert Forkel, Terhi Honkola, Gerson Klumpp, Richard Kowalik, Helle Metslang, Karl Pajusalu, Minerva Piha, Eva Saar, Sirkka Saarinen, Outi Vesakoski</t>
+  </si>
+  <si>
+    <t>CrossGram-SzetoYurayong2021</t>
+  </si>
+  <si>
+    <t>The CrossGram contribution "Sinitic between Altaic and Mainland Southeast Asia" is based on the data from Szeto &amp; Yurayong (2021) ("Sinitic as a typological sandwich: Revisiting the notions of Altaicization and Taicization", Linguistic Typology). (https://crossgram.clld.org/contributions/siniticbetween)</t>
   </si>
 </sst>
 </file>
@@ -349,6 +364,37 @@
         <v>31</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s" s="7">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s" s="9">
+        <v>33</v>
+      </c>
+      <c r="E9" s="10">
+        <v>2023</v>
+      </c>
+      <c r="F9" t="s" s="11">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s" s="7">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s" s="9">
+        <v>36</v>
+      </c>
+      <c r="E10" s="10">
+        <v>2021</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/raw/Feature_lists.xlsx
+++ b/raw/Feature_lists.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>id</t>
   </si>
@@ -83,6 +83,9 @@
     <t>David Inman et al. (https://atlas.evolvinglanguage.ch)</t>
   </si>
   <si>
+    <t>David Inman, Marine Vuillermet, and others</t>
+  </si>
+  <si>
     <t>CrossGram-Nichols1992</t>
   </si>
   <si>
@@ -110,7 +113,7 @@
     <t>UraTyp</t>
   </si>
   <si>
-    <t>UraTyp (Uralic Areal Typology Online) is a typological database with 360 features mainly on morphology, syntax, and phonology collected from 35 Uralic languages/language varieties. The database grew out from the cooperation with the Grambank team who set out to collect data from about half of the world's languages. The goal of building the UraTyp database was to create a family-specific database. (URL: https://uralic.clld.org/)</t>
+    <t>UraTyp (Uralic Areal Typology Online) is a typological database with 360 features mainly on morphology, syntax, and phonology collected from 35 Uralic languages/language varieties (Norvik et al. 2022). The database grew out from the cooperation with the Grambank team who set out to collect data from about half of the world's languages. The goal of building the UraTyp database was to create a family-specific database. (URL: https://uralic.clld.org/)</t>
   </si>
   <si>
     <t>Miina Norvik, Yingqi Jing, Michael Dunn, Robert Forkel, Terhi Honkola, Gerson Klumpp, Richard Kowalik, Helle Metslang, Karl Pajusalu, Minerva Piha, Eva Saar, Sirkka Saarinen, Outi Vesakoski</t>
@@ -120,6 +123,9 @@
   </si>
   <si>
     <t>The CrossGram contribution "Sinitic between Altaic and Mainland Southeast Asia" is based on the data from Szeto &amp; Yurayong (2021) ("Sinitic as a typological sandwich: Revisiting the notions of Altaicization and Taicization", Linguistic Typology). (https://crossgram.clld.org/contributions/siniticbetween)</t>
+  </si>
+  <si>
+    <t>Pui Yiu Szeto and Chingduang Yurayong</t>
   </si>
 </sst>
 </file>
@@ -323,25 +329,28 @@
       <c r="E6" s="10">
         <v>2025</v>
       </c>
+      <c r="F6" t="s" s="11">
+        <v>24</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6">
         <v>10</v>
       </c>
       <c r="B7" t="s" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s" s="8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s" s="9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="10">
         <v>1992</v>
       </c>
       <c r="F7" t="s" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -349,19 +358,19 @@
         <v>11</v>
       </c>
       <c r="B8" t="s" s="7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s" s="8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" s="10">
         <v>1997</v>
       </c>
       <c r="F8" t="s" s="11">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -369,16 +378,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="s" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" s="10">
         <v>2023</v>
       </c>
       <c r="F9" t="s" s="11">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -386,13 +395,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="s" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" s="10">
         <v>2021</v>
+      </c>
+      <c r="F10" t="s" s="11">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/raw/Feature_lists.xlsx
+++ b/raw/Feature_lists.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>id</t>
   </si>
@@ -29,6 +29,9 @@
     <t>Collection contributors</t>
   </si>
   <si>
+    <t>DOI</t>
+  </si>
+  <si>
     <t>SAILS</t>
   </si>
   <si>
@@ -41,6 +44,9 @@
     <t>Pieter Muysken, Harald Hammarström, Olga Krasnoukhova, Neele Müller, Joshua Birchall, Simon van de Kerke, Loretta O'Connor, Swintha Danielsen, Rik van Gijn, George Saad</t>
   </si>
   <si>
+    <t>https://doi.org/10.5281/zenodo.3608862</t>
+  </si>
+  <si>
     <t>WALS</t>
   </si>
   <si>
@@ -53,6 +59,9 @@
     <t>Matthew Dryer, Martin Haspelmath, David Gil, Bernard Comrie, Leon Stassen, Anna Siewierska, Dik Bakker, Balthasar Bickel, Johanna Nichols, Östen Dahl, Ian Maddieson, Johan van der Auwera, Harry van der Hulst, Sonia Cristofaro, Viveka Velupillai, and many others</t>
   </si>
   <si>
+    <t>https://doi.org/10.5281/zenodo.13950591</t>
+  </si>
+  <si>
     <t>Grambank</t>
   </si>
   <si>
@@ -65,15 +74,24 @@
     <t>Hedvig Skirgård, Hannah Haynie, Jakob Lesage, Jay Latarche, Alena Witzlack-Makarevich</t>
   </si>
   <si>
+    <t>https://doi.org/10.5281/zenodo.7844558</t>
+  </si>
+  <si>
     <t>APiCS</t>
   </si>
   <si>
+    <t>https://apics-online.info/</t>
+  </si>
+  <si>
     <t>APiCS (Atlas of Pidgin and Creole Language Structues) is a collection edited by Susanne Maria Michaelis, Philippe Maurer, Martin Haspelmath, Magnus Huber (https://apics-online.info). It was published by MPI-EVA in 2013, as well as in book form by Oxford University Press. In addition to the four editors, there are over 80 data contributors.</t>
   </si>
   <si>
     <t>Susanne Maria Michaelis, Philippe Maurer, Martin Haspelmath, Magnus Huber</t>
   </si>
   <si>
+    <t>https://doi.org/10.5281/zenodo.3823888</t>
+  </si>
+  <si>
     <t>ATLAs Zurich</t>
   </si>
   <si>
@@ -86,6 +104,9 @@
     <t>David Inman, Marine Vuillermet, and others</t>
   </si>
   <si>
+    <t>https://doi.org/10.5281/zenodo.15227808</t>
+  </si>
+  <si>
     <t>CrossGram-Nichols1992</t>
   </si>
   <si>
@@ -98,6 +119,9 @@
     <t>Johanna Nichols</t>
   </si>
   <si>
+    <t>https://doi.org/10.5281/zenodo.13831931</t>
+  </si>
+  <si>
     <t>CrossGram-Haspelmath1997i</t>
   </si>
   <si>
@@ -110,29 +134,59 @@
     <t>Martin Haspelmath</t>
   </si>
   <si>
+    <t>https://doi.org/10.5281/zenodo.17985706</t>
+  </si>
+  <si>
     <t>UraTyp</t>
   </si>
   <si>
+    <t>https://uralic.clld.org/</t>
+  </si>
+  <si>
     <t>UraTyp (Uralic Areal Typology Online) is a typological database with 360 features mainly on morphology, syntax, and phonology collected from 35 Uralic languages/language varieties (Norvik et al. 2022). The database grew out from the cooperation with the Grambank team who set out to collect data from about half of the world's languages. The goal of building the UraTyp database was to create a family-specific database. (URL: https://uralic.clld.org/)</t>
   </si>
   <si>
     <t>Miina Norvik, Yingqi Jing, Michael Dunn, Robert Forkel, Terhi Honkola, Gerson Klumpp, Richard Kowalik, Helle Metslang, Karl Pajusalu, Minerva Piha, Eva Saar, Sirkka Saarinen, Outi Vesakoski</t>
   </si>
   <si>
+    <t>https://doi.org/10.5281/zenodo.6392555</t>
+  </si>
+  <si>
     <t>CrossGram-SzetoYurayong2021</t>
   </si>
   <si>
+    <t>https://crossgram.clld.org/contributions/siniticbetween</t>
+  </si>
+  <si>
     <t>The CrossGram contribution "Sinitic between Altaic and Mainland Southeast Asia" is based on the data from Szeto &amp; Yurayong (2021) ("Sinitic as a typological sandwich: Revisiting the notions of Altaicization and Taicization", Linguistic Typology). (https://crossgram.clld.org/contributions/siniticbetween)</t>
   </si>
   <si>
     <t>Pui Yiu Szeto and Chingduang Yurayong</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.17986053</t>
+  </si>
+  <si>
+    <t>CrossGram-Kortmann1997</t>
+  </si>
+  <si>
+    <t>https://crossgram.clld.org/contributions/kortmannadverbial</t>
+  </si>
+  <si>
+    <t>The CrossGram contribution "Adverbial subordinators in European languages" is based on the data collected for Kortmann (1997), the first typological monograph about adverbial subordinators. (https://crossgram.clld.org/contributions/kortmannadverbial)</t>
+  </si>
+  <si>
+    <t>Bernd Kortmann</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.17985692</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt formatCode="@" numFmtId="165"/>
     <numFmt formatCode="mm/dd/yyyy" numFmtId="166"/>
     <numFmt formatCode="[hh]:mm:ss" numFmtId="167"/>
@@ -140,6 +194,7 @@
     <numFmt formatCode="@" numFmtId="170"/>
     <numFmt formatCode="@" numFmtId="171"/>
     <numFmt formatCode="@" numFmtId="173"/>
+    <numFmt formatCode="@" numFmtId="174"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -175,7 +230,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -206,6 +261,9 @@
       <alignment horizontal="general" vertical="top"/>
     </xf>
     <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0">
+      <alignment horizontal="general" vertical="top"/>
+    </xf>
+    <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="174" xfId="0">
       <alignment horizontal="general" vertical="top"/>
     </xf>
   </cellXfs>
@@ -235,25 +293,31 @@
       <c r="F1" t="s" s="1">
         <v>5</v>
       </c>
+      <c r="G1" t="s" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
       <c r="B2" t="s" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="10">
         <v>2016</v>
       </c>
       <c r="F2" t="s" s="11">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="G2" t="s" s="12">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -261,19 +325,22 @@
         <v>3</v>
       </c>
       <c r="B3" t="s" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s" s="8">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s" s="9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="10">
         <v>2013</v>
       </c>
       <c r="F3" t="s" s="11">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="12">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -281,19 +348,22 @@
         <v>4</v>
       </c>
       <c r="B4" t="s" s="7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s" s="8">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s" s="9">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" s="10">
         <v>2023</v>
       </c>
       <c r="F4" t="s" s="11">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="G4" t="s" s="12">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -301,16 +371,22 @@
         <v>1</v>
       </c>
       <c r="B5" t="s" s="7">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="C5" t="s" s="8">
+        <v>23</v>
       </c>
       <c r="D5" t="s" s="9">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E5" s="10">
         <v>2013</v>
       </c>
       <c r="F5" t="s" s="11">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="G5" t="s" s="12">
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -318,19 +394,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s" s="7">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s" s="8">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s" s="9">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E6" s="10">
         <v>2025</v>
       </c>
       <c r="F6" t="s" s="11">
-        <v>24</v>
+        <v>30</v>
+      </c>
+      <c r="G6" t="s" s="12">
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -338,19 +417,22 @@
         <v>10</v>
       </c>
       <c r="B7" t="s" s="7">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s" s="8">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s" s="9">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E7" s="10">
         <v>1992</v>
       </c>
       <c r="F7" t="s" s="11">
-        <v>28</v>
+        <v>35</v>
+      </c>
+      <c r="G7" t="s" s="12">
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -358,19 +440,22 @@
         <v>11</v>
       </c>
       <c r="B8" t="s" s="7">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s" s="8">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s" s="9">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E8" s="10">
         <v>1997</v>
       </c>
       <c r="F8" t="s" s="11">
-        <v>32</v>
+        <v>40</v>
+      </c>
+      <c r="G8" t="s" s="12">
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -378,16 +463,22 @@
         <v>12</v>
       </c>
       <c r="B9" t="s" s="7">
-        <v>33</v>
+        <v>42</v>
+      </c>
+      <c r="C9" t="s" s="8">
+        <v>43</v>
       </c>
       <c r="D9" t="s" s="9">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E9" s="10">
         <v>2023</v>
       </c>
       <c r="F9" t="s" s="11">
-        <v>35</v>
+        <v>45</v>
+      </c>
+      <c r="G9" t="s" s="12">
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -395,16 +486,45 @@
         <v>13</v>
       </c>
       <c r="B10" t="s" s="7">
-        <v>36</v>
+        <v>47</v>
+      </c>
+      <c r="C10" t="s" s="8">
+        <v>48</v>
       </c>
       <c r="D10" t="s" s="9">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E10" s="10">
         <v>2021</v>
       </c>
       <c r="F10" t="s" s="11">
-        <v>38</v>
+        <v>50</v>
+      </c>
+      <c r="G10" t="s" s="12">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s" s="8">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s" s="9">
+        <v>54</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1997</v>
+      </c>
+      <c r="F11" t="s" s="11">
+        <v>55</v>
+      </c>
+      <c r="G11" t="s" s="12">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
